--- a/artfynd/A 70501-2021 artfynd.xlsx
+++ b/artfynd/A 70501-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 70501-2021 artfynd.xlsx
+++ b/artfynd/A 70501-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>91940105</v>
       </c>
       <c r="B2" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576957.5210313153</v>
+        <v>576958</v>
       </c>
       <c r="R2" t="n">
-        <v>6556037.953185718</v>
+        <v>6556038</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-03-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-03-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,37 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91939778</v>
+        <v>91940106</v>
       </c>
       <c r="B3" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576957.5210313153</v>
+        <v>576930</v>
       </c>
       <c r="R3" t="n">
-        <v>6556037.953185718</v>
+        <v>6556098</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,21 +855,11 @@
           <t>2021-03-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-03-26</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -901,7 +871,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>blandskog med grova tallar</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -926,6 +896,477 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>91939778</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lörens östra sida, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>576958</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6556038</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-03-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-03-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>blandskog med grova tallar</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>91939779</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lörens östra sida, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>576930</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6556098</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-03-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-03-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129084521</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lören, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>576905</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6556142</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Växte vid gamla tallar</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Helena  Andresson Tsiamanis</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Helena  Andresson Tsiamanis</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127311992</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57754</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fjellskäfte, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>577057</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6556012</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jeroen de Vries</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jeroen de Vries</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 70501-2021 artfynd.xlsx
+++ b/artfynd/A 70501-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91940105</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91940106</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91939778</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91939779</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1244,6 +1269,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129084521</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1367,8 +1397,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127311992</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>